--- a/mock_question_bank_template.xlsx
+++ b/mock_question_bank_template.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +27,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEBFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,56 +428,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Part</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Passage ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Question No</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Passage</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
@@ -471,46 +504,312 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>EVS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAT_PATTERN</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Sample question</t>
-        </is>
-      </c>
+          <t>EVS_MCQ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sample EVS question</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Option A</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Option D</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EVS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EVS_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EVS-P01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>First question based on the passage</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EVS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EVS_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EVS-P01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Second question based on the passage</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Passage ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Passage Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Passage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EVS-P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EVS Passage 1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Paste the complete passage here once. Link its five questions to EVS-P01 in the Questions sheet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Bulk Mock Question Upload</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Use this workbook for EVS and Language.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Normal MCQ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Use Questions sheet; leave Passage ID blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Passage + 5 Questions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Add one row in Passages, then five question rows in Questions using the same Passage ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Allowed Parts</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EVS_MCQ, EVS_PASSAGE, LANG_P1, LANG_P2, LANG_P3, LANG_P4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Images</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Image URL may be left blank. Teacher can add/replace an image later from Manage Question Bank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Use only A, B, C or D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MAT / Arithmetic</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Use the PDF + Answer Key upload instead of this Excel workbook.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
